--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676944</v>
+        <v>119676942</v>
       </c>
       <c r="B16" t="n">
-        <v>57326</v>
+        <v>79636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887447</v>
+        <v>887583</v>
       </c>
       <c r="R16" t="n">
-        <v>7417846</v>
+        <v>7417869</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676942</v>
+        <v>119676944</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887583</v>
+        <v>887447</v>
       </c>
       <c r="R17" t="n">
-        <v>7417869</v>
+        <v>7417846</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676953</v>
+        <v>119676966</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887516</v>
+        <v>887446</v>
       </c>
       <c r="R39" t="n">
-        <v>7417853</v>
+        <v>7417848</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676966</v>
+        <v>119676953</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887446</v>
+        <v>887516</v>
       </c>
       <c r="R40" t="n">
-        <v>7417848</v>
+        <v>7417853</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676960</v>
+        <v>119676968</v>
       </c>
       <c r="B41" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4665,25 +4665,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887308</v>
+        <v>887375</v>
       </c>
       <c r="R41" t="n">
-        <v>7417790</v>
+        <v>7417827</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676968</v>
+        <v>119676960</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4767,25 +4767,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887375</v>
+        <v>887308</v>
       </c>
       <c r="R42" t="n">
-        <v>7417827</v>
+        <v>7417790</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119676954</v>
+        <v>119676971</v>
       </c>
       <c r="B36" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4155,25 +4155,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887529</v>
+        <v>887491</v>
       </c>
       <c r="R36" t="n">
-        <v>7417855</v>
+        <v>7417873</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119676974</v>
+        <v>119676954</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887376</v>
+        <v>887529</v>
       </c>
       <c r="R37" t="n">
-        <v>7417815</v>
+        <v>7417855</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119676971</v>
+        <v>119676974</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4359,25 +4359,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887491</v>
+        <v>887376</v>
       </c>
       <c r="R38" t="n">
-        <v>7417873</v>
+        <v>7417815</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676966</v>
+        <v>119676953</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887446</v>
+        <v>887516</v>
       </c>
       <c r="R39" t="n">
-        <v>7417848</v>
+        <v>7417853</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676953</v>
+        <v>119676966</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887516</v>
+        <v>887446</v>
       </c>
       <c r="R40" t="n">
-        <v>7417853</v>
+        <v>7417848</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676948</v>
+        <v>119676938</v>
       </c>
       <c r="B2" t="n">
-        <v>79635</v>
+        <v>79636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887316</v>
+        <v>887506</v>
       </c>
       <c r="R2" t="n">
-        <v>7417879</v>
+        <v>7417868</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676936</v>
+        <v>119676952</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887699</v>
+        <v>887513</v>
       </c>
       <c r="R3" t="n">
-        <v>7417852</v>
+        <v>7417863</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676951</v>
+        <v>119676941</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887490</v>
+        <v>887587</v>
       </c>
       <c r="R4" t="n">
-        <v>7417868</v>
+        <v>7417852</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676927</v>
+        <v>119676940</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>79636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887487</v>
+        <v>887549</v>
       </c>
       <c r="R5" t="n">
-        <v>7417829</v>
+        <v>7417846</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676932</v>
+        <v>119676943</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887564</v>
+        <v>887593</v>
       </c>
       <c r="R6" t="n">
-        <v>7417841</v>
+        <v>7417886</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676943</v>
+        <v>119676925</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887593</v>
+        <v>887694</v>
       </c>
       <c r="R7" t="n">
-        <v>7417886</v>
+        <v>7417854</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676930</v>
+        <v>119676927</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887519</v>
+        <v>887487</v>
       </c>
       <c r="R8" t="n">
-        <v>7417814</v>
+        <v>7417829</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676947</v>
+        <v>119676944</v>
       </c>
       <c r="B9" t="n">
-        <v>90846</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887690</v>
+        <v>887447</v>
       </c>
       <c r="R9" t="n">
-        <v>7417856</v>
+        <v>7417846</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676941</v>
+        <v>119676931</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887587</v>
+        <v>887530</v>
       </c>
       <c r="R10" t="n">
-        <v>7417852</v>
+        <v>7417857</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676938</v>
+        <v>119676948</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>79635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887506</v>
+        <v>887316</v>
       </c>
       <c r="R11" t="n">
-        <v>7417868</v>
+        <v>7417879</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676939</v>
+        <v>119676930</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887530</v>
+        <v>887519</v>
       </c>
       <c r="R12" t="n">
-        <v>7417856</v>
+        <v>7417814</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676931</v>
+        <v>119676937</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887530</v>
+        <v>887647</v>
       </c>
       <c r="R13" t="n">
-        <v>7417857</v>
+        <v>7417821</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676952</v>
+        <v>119676932</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887513</v>
+        <v>887564</v>
       </c>
       <c r="R14" t="n">
-        <v>7417863</v>
+        <v>7417841</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676926</v>
+        <v>119676951</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887484</v>
+        <v>887490</v>
       </c>
       <c r="R15" t="n">
-        <v>7417825</v>
+        <v>7417868</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676944</v>
+        <v>119676936</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>79636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887447</v>
+        <v>887699</v>
       </c>
       <c r="R17" t="n">
-        <v>7417846</v>
+        <v>7417852</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676925</v>
+        <v>119676929</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887694</v>
+        <v>887625</v>
       </c>
       <c r="R18" t="n">
-        <v>7417854</v>
+        <v>7417880</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676937</v>
+        <v>119676926</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887647</v>
+        <v>887484</v>
       </c>
       <c r="R19" t="n">
-        <v>7417821</v>
+        <v>7417825</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676940</v>
+        <v>119676947</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>90846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887549</v>
+        <v>887690</v>
       </c>
       <c r="R20" t="n">
-        <v>7417846</v>
+        <v>7417856</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676929</v>
+        <v>119676939</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887625</v>
+        <v>887530</v>
       </c>
       <c r="R21" t="n">
-        <v>7417880</v>
+        <v>7417856</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676959</v>
+        <v>119676970</v>
       </c>
       <c r="B22" t="n">
-        <v>79643</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887484</v>
+        <v>887373</v>
       </c>
       <c r="R22" t="n">
-        <v>7417813</v>
+        <v>7417870</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676967</v>
+        <v>119676958</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887389</v>
+        <v>887619</v>
       </c>
       <c r="R23" t="n">
-        <v>7417834</v>
+        <v>7417836</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676958</v>
+        <v>119676959</v>
       </c>
       <c r="B24" t="n">
         <v>79643</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887619</v>
+        <v>887484</v>
       </c>
       <c r="R24" t="n">
-        <v>7417836</v>
+        <v>7417813</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676961</v>
+        <v>119676953</v>
       </c>
       <c r="B25" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887272</v>
+        <v>887516</v>
       </c>
       <c r="R25" t="n">
-        <v>7417781</v>
+        <v>7417853</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676973</v>
+        <v>119676969</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887588</v>
+        <v>887366</v>
       </c>
       <c r="R26" t="n">
-        <v>7417887</v>
+        <v>7417866</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676977</v>
+        <v>119676954</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887608</v>
+        <v>887529</v>
       </c>
       <c r="R27" t="n">
-        <v>7417884</v>
+        <v>7417855</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676956</v>
+        <v>119676977</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887549</v>
+        <v>887608</v>
       </c>
       <c r="R28" t="n">
-        <v>7417845</v>
+        <v>7417884</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676970</v>
+        <v>119676957</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887373</v>
+        <v>887564</v>
       </c>
       <c r="R29" t="n">
-        <v>7417870</v>
+        <v>7417841</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676969</v>
+        <v>119676968</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887366</v>
+        <v>887375</v>
       </c>
       <c r="R30" t="n">
-        <v>7417866</v>
+        <v>7417827</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676963</v>
+        <v>119676961</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3645,25 +3645,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887685</v>
+        <v>887272</v>
       </c>
       <c r="R31" t="n">
-        <v>7417879</v>
+        <v>7417781</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119676975</v>
+        <v>119676976</v>
       </c>
       <c r="B32" t="n">
         <v>78526</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887451</v>
+        <v>887509</v>
       </c>
       <c r="R32" t="n">
-        <v>7417867</v>
+        <v>7417861</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119676979</v>
+        <v>119676975</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887276</v>
+        <v>887451</v>
       </c>
       <c r="R33" t="n">
-        <v>7417801</v>
+        <v>7417867</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119676972</v>
+        <v>119676963</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887564</v>
+        <v>887685</v>
       </c>
       <c r="R35" t="n">
-        <v>7417841</v>
+        <v>7417879</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119676971</v>
+        <v>119676967</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887491</v>
+        <v>887389</v>
       </c>
       <c r="R36" t="n">
-        <v>7417873</v>
+        <v>7417834</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119676954</v>
+        <v>119676972</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887529</v>
+        <v>887564</v>
       </c>
       <c r="R37" t="n">
-        <v>7417855</v>
+        <v>7417841</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119676974</v>
+        <v>119676966</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4359,25 +4359,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887376</v>
+        <v>887446</v>
       </c>
       <c r="R38" t="n">
-        <v>7417815</v>
+        <v>7417848</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676953</v>
+        <v>119676973</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887516</v>
+        <v>887588</v>
       </c>
       <c r="R39" t="n">
-        <v>7417853</v>
+        <v>7417887</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676966</v>
+        <v>119676974</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887446</v>
+        <v>887376</v>
       </c>
       <c r="R40" t="n">
-        <v>7417848</v>
+        <v>7417815</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676968</v>
+        <v>119676971</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887375</v>
+        <v>887491</v>
       </c>
       <c r="R41" t="n">
-        <v>7417827</v>
+        <v>7417873</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676960</v>
+        <v>119676956</v>
       </c>
       <c r="B42" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887308</v>
+        <v>887549</v>
       </c>
       <c r="R42" t="n">
-        <v>7417790</v>
+        <v>7417845</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119676957</v>
+        <v>119676979</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887564</v>
+        <v>887276</v>
       </c>
       <c r="R43" t="n">
-        <v>7417841</v>
+        <v>7417801</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119676976</v>
+        <v>119676960</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887509</v>
+        <v>887308</v>
       </c>
       <c r="R44" t="n">
-        <v>7417861</v>
+        <v>7417790</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676932</v>
+        <v>119676942</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887564</v>
+        <v>887583</v>
       </c>
       <c r="R14" t="n">
-        <v>7417841</v>
+        <v>7417869</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676951</v>
+        <v>119676936</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887490</v>
+        <v>887699</v>
       </c>
       <c r="R15" t="n">
-        <v>7417868</v>
+        <v>7417852</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676942</v>
+        <v>119676951</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887583</v>
+        <v>887490</v>
       </c>
       <c r="R16" t="n">
-        <v>7417869</v>
+        <v>7417868</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676936</v>
+        <v>119676932</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887699</v>
+        <v>887564</v>
       </c>
       <c r="R17" t="n">
-        <v>7417852</v>
+        <v>7417841</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676938</v>
+        <v>119676941</v>
       </c>
       <c r="B2" t="n">
         <v>79636</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887506</v>
+        <v>887587</v>
       </c>
       <c r="R2" t="n">
-        <v>7417868</v>
+        <v>7417852</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676952</v>
+        <v>119676942</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887513</v>
+        <v>887583</v>
       </c>
       <c r="R3" t="n">
-        <v>7417863</v>
+        <v>7417869</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676941</v>
+        <v>119676944</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887587</v>
+        <v>887447</v>
       </c>
       <c r="R4" t="n">
-        <v>7417852</v>
+        <v>7417846</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676940</v>
+        <v>119676931</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887549</v>
+        <v>887530</v>
       </c>
       <c r="R5" t="n">
-        <v>7417846</v>
+        <v>7417857</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676943</v>
+        <v>119676929</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887593</v>
+        <v>887625</v>
       </c>
       <c r="R6" t="n">
-        <v>7417886</v>
+        <v>7417880</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676925</v>
+        <v>119676951</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887694</v>
+        <v>887490</v>
       </c>
       <c r="R7" t="n">
-        <v>7417854</v>
+        <v>7417868</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676927</v>
+        <v>119676939</v>
       </c>
       <c r="B8" t="n">
-        <v>91254</v>
+        <v>79636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887487</v>
+        <v>887530</v>
       </c>
       <c r="R8" t="n">
-        <v>7417829</v>
+        <v>7417856</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676944</v>
+        <v>119676932</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887447</v>
+        <v>887564</v>
       </c>
       <c r="R9" t="n">
-        <v>7417846</v>
+        <v>7417841</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676931</v>
+        <v>119676943</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887530</v>
+        <v>887593</v>
       </c>
       <c r="R10" t="n">
-        <v>7417857</v>
+        <v>7417886</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676948</v>
+        <v>119676937</v>
       </c>
       <c r="B11" t="n">
-        <v>79635</v>
+        <v>79636</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887316</v>
+        <v>887647</v>
       </c>
       <c r="R11" t="n">
-        <v>7417879</v>
+        <v>7417821</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676930</v>
+        <v>119676947</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887519</v>
+        <v>887690</v>
       </c>
       <c r="R12" t="n">
-        <v>7417814</v>
+        <v>7417856</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676937</v>
+        <v>119676938</v>
       </c>
       <c r="B13" t="n">
         <v>79636</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887647</v>
+        <v>887506</v>
       </c>
       <c r="R13" t="n">
-        <v>7417821</v>
+        <v>7417868</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676942</v>
+        <v>119676927</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>91254</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887583</v>
+        <v>887487</v>
       </c>
       <c r="R14" t="n">
-        <v>7417869</v>
+        <v>7417829</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676936</v>
+        <v>119676930</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887699</v>
+        <v>887519</v>
       </c>
       <c r="R15" t="n">
-        <v>7417852</v>
+        <v>7417814</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676951</v>
+        <v>119676926</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887490</v>
+        <v>887484</v>
       </c>
       <c r="R16" t="n">
-        <v>7417868</v>
+        <v>7417825</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676932</v>
+        <v>119676940</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887564</v>
+        <v>887549</v>
       </c>
       <c r="R17" t="n">
-        <v>7417841</v>
+        <v>7417846</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676929</v>
+        <v>119676925</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887625</v>
+        <v>887694</v>
       </c>
       <c r="R18" t="n">
-        <v>7417880</v>
+        <v>7417854</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676926</v>
+        <v>119676952</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887484</v>
+        <v>887513</v>
       </c>
       <c r="R19" t="n">
-        <v>7417825</v>
+        <v>7417863</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676947</v>
+        <v>119676948</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>79635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887690</v>
+        <v>887316</v>
       </c>
       <c r="R20" t="n">
-        <v>7417856</v>
+        <v>7417879</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676939</v>
+        <v>119676936</v>
       </c>
       <c r="B21" t="n">
         <v>79636</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887530</v>
+        <v>887699</v>
       </c>
       <c r="R21" t="n">
-        <v>7417856</v>
+        <v>7417852</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676970</v>
+        <v>119676959</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887373</v>
+        <v>887484</v>
       </c>
       <c r="R22" t="n">
-        <v>7417870</v>
+        <v>7417813</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676958</v>
+        <v>119676954</v>
       </c>
       <c r="B23" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887619</v>
+        <v>887529</v>
       </c>
       <c r="R23" t="n">
-        <v>7417836</v>
+        <v>7417855</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676959</v>
+        <v>119676970</v>
       </c>
       <c r="B24" t="n">
-        <v>79643</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887484</v>
+        <v>887373</v>
       </c>
       <c r="R24" t="n">
-        <v>7417813</v>
+        <v>7417870</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676953</v>
+        <v>119676967</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887516</v>
+        <v>887389</v>
       </c>
       <c r="R25" t="n">
-        <v>7417853</v>
+        <v>7417834</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676954</v>
+        <v>119676956</v>
       </c>
       <c r="B27" t="n">
         <v>79607</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887529</v>
+        <v>887549</v>
       </c>
       <c r="R27" t="n">
-        <v>7417855</v>
+        <v>7417845</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676977</v>
+        <v>119676971</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887608</v>
+        <v>887491</v>
       </c>
       <c r="R28" t="n">
-        <v>7417884</v>
+        <v>7417873</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676957</v>
+        <v>119676976</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887564</v>
+        <v>887509</v>
       </c>
       <c r="R29" t="n">
-        <v>7417841</v>
+        <v>7417861</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676968</v>
+        <v>119676975</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3543,25 +3543,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887375</v>
+        <v>887451</v>
       </c>
       <c r="R30" t="n">
-        <v>7417827</v>
+        <v>7417867</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676961</v>
+        <v>119676957</v>
       </c>
       <c r="B31" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887272</v>
+        <v>887564</v>
       </c>
       <c r="R31" t="n">
-        <v>7417781</v>
+        <v>7417841</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119676976</v>
+        <v>119676973</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3747,25 +3747,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887509</v>
+        <v>887588</v>
       </c>
       <c r="R32" t="n">
-        <v>7417861</v>
+        <v>7417887</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119676975</v>
+        <v>119676960</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887451</v>
+        <v>887308</v>
       </c>
       <c r="R33" t="n">
-        <v>7417867</v>
+        <v>7417790</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119676964</v>
+        <v>119676961</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3951,25 +3951,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887527</v>
+        <v>887272</v>
       </c>
       <c r="R34" t="n">
-        <v>7417856</v>
+        <v>7417781</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119676967</v>
+        <v>119676979</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>78171</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4155,25 +4155,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887389</v>
+        <v>887276</v>
       </c>
       <c r="R36" t="n">
-        <v>7417834</v>
+        <v>7417801</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119676972</v>
+        <v>119676966</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887564</v>
+        <v>887446</v>
       </c>
       <c r="R37" t="n">
-        <v>7417841</v>
+        <v>7417848</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119676966</v>
+        <v>119676974</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4359,25 +4359,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887446</v>
+        <v>887376</v>
       </c>
       <c r="R38" t="n">
-        <v>7417848</v>
+        <v>7417815</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676973</v>
+        <v>119676953</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887588</v>
+        <v>887516</v>
       </c>
       <c r="R39" t="n">
-        <v>7417887</v>
+        <v>7417853</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676974</v>
+        <v>119676958</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887376</v>
+        <v>887619</v>
       </c>
       <c r="R40" t="n">
-        <v>7417815</v>
+        <v>7417836</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676971</v>
+        <v>119676977</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4665,25 +4665,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887491</v>
+        <v>887608</v>
       </c>
       <c r="R41" t="n">
-        <v>7417873</v>
+        <v>7417884</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676956</v>
+        <v>119676972</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4767,25 +4767,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887549</v>
+        <v>887564</v>
       </c>
       <c r="R42" t="n">
-        <v>7417845</v>
+        <v>7417841</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119676979</v>
+        <v>119676964</v>
       </c>
       <c r="B43" t="n">
-        <v>78171</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4869,25 +4869,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887276</v>
+        <v>887527</v>
       </c>
       <c r="R43" t="n">
-        <v>7417801</v>
+        <v>7417856</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119676960</v>
+        <v>119676968</v>
       </c>
       <c r="B44" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4971,25 +4971,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887308</v>
+        <v>887375</v>
       </c>
       <c r="R44" t="n">
-        <v>7417790</v>
+        <v>7417827</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676967</v>
+        <v>119676956</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887389</v>
+        <v>887549</v>
       </c>
       <c r="R25" t="n">
-        <v>7417834</v>
+        <v>7417845</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676969</v>
+        <v>119676967</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887366</v>
+        <v>887389</v>
       </c>
       <c r="R26" t="n">
-        <v>7417866</v>
+        <v>7417834</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676956</v>
+        <v>119676969</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887549</v>
+        <v>887366</v>
       </c>
       <c r="R27" t="n">
-        <v>7417845</v>
+        <v>7417866</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676958</v>
+        <v>119676972</v>
       </c>
       <c r="B40" t="n">
-        <v>79643</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887619</v>
+        <v>887564</v>
       </c>
       <c r="R40" t="n">
-        <v>7417836</v>
+        <v>7417841</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676977</v>
+        <v>119676964</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4665,25 +4665,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887608</v>
+        <v>887527</v>
       </c>
       <c r="R41" t="n">
-        <v>7417884</v>
+        <v>7417856</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676972</v>
+        <v>119676977</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4767,25 +4767,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887564</v>
+        <v>887608</v>
       </c>
       <c r="R42" t="n">
-        <v>7417841</v>
+        <v>7417884</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119676964</v>
+        <v>119676958</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4869,25 +4869,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887527</v>
+        <v>887619</v>
       </c>
       <c r="R43" t="n">
-        <v>7417856</v>
+        <v>7417836</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676941</v>
+        <v>119676936</v>
       </c>
       <c r="B2" t="n">
         <v>79636</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887587</v>
+        <v>887699</v>
       </c>
       <c r="R2" t="n">
         <v>7417852</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676942</v>
+        <v>119676925</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887583</v>
+        <v>887694</v>
       </c>
       <c r="R3" t="n">
-        <v>7417869</v>
+        <v>7417854</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676944</v>
+        <v>119676940</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>79636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887447</v>
+        <v>887549</v>
       </c>
       <c r="R4" t="n">
         <v>7417846</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676931</v>
+        <v>119676941</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887530</v>
+        <v>887587</v>
       </c>
       <c r="R5" t="n">
-        <v>7417857</v>
+        <v>7417852</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676929</v>
+        <v>119676944</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887625</v>
+        <v>887447</v>
       </c>
       <c r="R6" t="n">
-        <v>7417880</v>
+        <v>7417846</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676951</v>
+        <v>119676926</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887490</v>
+        <v>887484</v>
       </c>
       <c r="R7" t="n">
-        <v>7417868</v>
+        <v>7417825</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676939</v>
+        <v>119676952</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887530</v>
+        <v>887513</v>
       </c>
       <c r="R8" t="n">
-        <v>7417856</v>
+        <v>7417863</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676932</v>
+        <v>119676927</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887564</v>
+        <v>887487</v>
       </c>
       <c r="R9" t="n">
-        <v>7417841</v>
+        <v>7417829</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676943</v>
+        <v>119676948</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>79635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887593</v>
+        <v>887316</v>
       </c>
       <c r="R10" t="n">
-        <v>7417886</v>
+        <v>7417879</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676937</v>
+        <v>119676938</v>
       </c>
       <c r="B11" t="n">
         <v>79636</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887647</v>
+        <v>887506</v>
       </c>
       <c r="R11" t="n">
-        <v>7417821</v>
+        <v>7417868</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676947</v>
+        <v>119676937</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>79636</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887690</v>
+        <v>887647</v>
       </c>
       <c r="R12" t="n">
-        <v>7417856</v>
+        <v>7417821</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676938</v>
+        <v>119676947</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>90846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887506</v>
+        <v>887690</v>
       </c>
       <c r="R13" t="n">
-        <v>7417868</v>
+        <v>7417856</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676927</v>
+        <v>119676939</v>
       </c>
       <c r="B14" t="n">
-        <v>91254</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887487</v>
+        <v>887530</v>
       </c>
       <c r="R14" t="n">
-        <v>7417829</v>
+        <v>7417856</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676930</v>
+        <v>119676942</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887519</v>
+        <v>887583</v>
       </c>
       <c r="R15" t="n">
-        <v>7417814</v>
+        <v>7417869</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676926</v>
+        <v>119676931</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887484</v>
+        <v>887530</v>
       </c>
       <c r="R16" t="n">
-        <v>7417825</v>
+        <v>7417857</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676940</v>
+        <v>119676951</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887549</v>
+        <v>887490</v>
       </c>
       <c r="R17" t="n">
-        <v>7417846</v>
+        <v>7417868</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676925</v>
+        <v>119676929</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887694</v>
+        <v>887625</v>
       </c>
       <c r="R18" t="n">
-        <v>7417854</v>
+        <v>7417880</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676952</v>
+        <v>119676943</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887513</v>
+        <v>887593</v>
       </c>
       <c r="R19" t="n">
-        <v>7417863</v>
+        <v>7417886</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676948</v>
+        <v>119676930</v>
       </c>
       <c r="B20" t="n">
-        <v>79635</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887316</v>
+        <v>887519</v>
       </c>
       <c r="R20" t="n">
-        <v>7417879</v>
+        <v>7417814</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676936</v>
+        <v>119676932</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887699</v>
+        <v>887564</v>
       </c>
       <c r="R21" t="n">
-        <v>7417852</v>
+        <v>7417841</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676959</v>
+        <v>119676958</v>
       </c>
       <c r="B22" t="n">
         <v>79643</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887484</v>
+        <v>887619</v>
       </c>
       <c r="R22" t="n">
-        <v>7417813</v>
+        <v>7417836</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676954</v>
+        <v>119676957</v>
       </c>
       <c r="B23" t="n">
         <v>79607</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887529</v>
+        <v>887564</v>
       </c>
       <c r="R23" t="n">
-        <v>7417855</v>
+        <v>7417841</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676970</v>
+        <v>119676956</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887373</v>
+        <v>887549</v>
       </c>
       <c r="R24" t="n">
-        <v>7417870</v>
+        <v>7417845</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676956</v>
+        <v>119676964</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887549</v>
+        <v>887527</v>
       </c>
       <c r="R25" t="n">
-        <v>7417845</v>
+        <v>7417856</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676967</v>
+        <v>119676968</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887389</v>
+        <v>887375</v>
       </c>
       <c r="R26" t="n">
-        <v>7417834</v>
+        <v>7417827</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676969</v>
+        <v>119676971</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887366</v>
+        <v>887491</v>
       </c>
       <c r="R27" t="n">
-        <v>7417866</v>
+        <v>7417873</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676971</v>
+        <v>119676972</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887491</v>
+        <v>887564</v>
       </c>
       <c r="R28" t="n">
-        <v>7417873</v>
+        <v>7417841</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676975</v>
+        <v>119676963</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3543,25 +3543,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887451</v>
+        <v>887685</v>
       </c>
       <c r="R30" t="n">
-        <v>7417867</v>
+        <v>7417879</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676957</v>
+        <v>119676953</v>
       </c>
       <c r="B31" t="n">
         <v>79607</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887564</v>
+        <v>887516</v>
       </c>
       <c r="R31" t="n">
-        <v>7417841</v>
+        <v>7417853</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119676973</v>
+        <v>119676961</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3747,25 +3747,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887588</v>
+        <v>887272</v>
       </c>
       <c r="R32" t="n">
-        <v>7417887</v>
+        <v>7417781</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119676960</v>
+        <v>119676973</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3849,25 +3849,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887308</v>
+        <v>887588</v>
       </c>
       <c r="R33" t="n">
-        <v>7417790</v>
+        <v>7417887</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119676961</v>
+        <v>119676959</v>
       </c>
       <c r="B34" t="n">
-        <v>78262</v>
+        <v>79643</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3951,25 +3951,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887272</v>
+        <v>887484</v>
       </c>
       <c r="R34" t="n">
-        <v>7417781</v>
+        <v>7417813</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119676963</v>
+        <v>119676969</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887685</v>
+        <v>887366</v>
       </c>
       <c r="R35" t="n">
-        <v>7417879</v>
+        <v>7417866</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119676966</v>
+        <v>119676954</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887446</v>
+        <v>887529</v>
       </c>
       <c r="R37" t="n">
-        <v>7417848</v>
+        <v>7417855</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676953</v>
+        <v>119676977</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887516</v>
+        <v>887608</v>
       </c>
       <c r="R39" t="n">
-        <v>7417853</v>
+        <v>7417884</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676972</v>
+        <v>119676975</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887564</v>
+        <v>887451</v>
       </c>
       <c r="R40" t="n">
-        <v>7417841</v>
+        <v>7417867</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676964</v>
+        <v>119676966</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887527</v>
+        <v>887446</v>
       </c>
       <c r="R41" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676977</v>
+        <v>119676970</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4767,25 +4767,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887608</v>
+        <v>887373</v>
       </c>
       <c r="R42" t="n">
-        <v>7417884</v>
+        <v>7417870</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119676958</v>
+        <v>119676960</v>
       </c>
       <c r="B43" t="n">
-        <v>79643</v>
+        <v>78262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4869,25 +4869,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887619</v>
+        <v>887308</v>
       </c>
       <c r="R43" t="n">
-        <v>7417836</v>
+        <v>7417790</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119676968</v>
+        <v>119676967</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887375</v>
+        <v>887389</v>
       </c>
       <c r="R44" t="n">
-        <v>7417827</v>
+        <v>7417834</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676972</v>
+        <v>119676976</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887564</v>
+        <v>887509</v>
       </c>
       <c r="R28" t="n">
-        <v>7417841</v>
+        <v>7417861</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676976</v>
+        <v>119676972</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887509</v>
+        <v>887564</v>
       </c>
       <c r="R29" t="n">
-        <v>7417861</v>
+        <v>7417841</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676977</v>
+        <v>119676966</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887608</v>
+        <v>887446</v>
       </c>
       <c r="R39" t="n">
-        <v>7417884</v>
+        <v>7417848</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676975</v>
+        <v>119676970</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887451</v>
+        <v>887373</v>
       </c>
       <c r="R40" t="n">
-        <v>7417867</v>
+        <v>7417870</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676966</v>
+        <v>119676977</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4665,25 +4665,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887446</v>
+        <v>887608</v>
       </c>
       <c r="R41" t="n">
-        <v>7417848</v>
+        <v>7417884</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676970</v>
+        <v>119676975</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4767,25 +4767,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887373</v>
+        <v>887451</v>
       </c>
       <c r="R42" t="n">
-        <v>7417870</v>
+        <v>7417867</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676947</v>
+        <v>119676939</v>
       </c>
       <c r="B13" t="n">
-        <v>90846</v>
+        <v>79636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887690</v>
+        <v>887530</v>
       </c>
       <c r="R13" t="n">
         <v>7417856</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676939</v>
+        <v>119676947</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>90846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887530</v>
+        <v>887690</v>
       </c>
       <c r="R14" t="n">
         <v>7417856</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676976</v>
+        <v>119676972</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887509</v>
+        <v>887564</v>
       </c>
       <c r="R28" t="n">
-        <v>7417861</v>
+        <v>7417841</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676972</v>
+        <v>119676976</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887564</v>
+        <v>887509</v>
       </c>
       <c r="R29" t="n">
-        <v>7417841</v>
+        <v>7417861</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676966</v>
+        <v>119676977</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887446</v>
+        <v>887608</v>
       </c>
       <c r="R39" t="n">
-        <v>7417848</v>
+        <v>7417884</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676970</v>
+        <v>119676975</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887373</v>
+        <v>887451</v>
       </c>
       <c r="R40" t="n">
-        <v>7417870</v>
+        <v>7417867</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676977</v>
+        <v>119676966</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4665,25 +4665,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887608</v>
+        <v>887446</v>
       </c>
       <c r="R41" t="n">
-        <v>7417884</v>
+        <v>7417848</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676975</v>
+        <v>119676970</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4767,25 +4767,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887451</v>
+        <v>887373</v>
       </c>
       <c r="R42" t="n">
-        <v>7417867</v>
+        <v>7417870</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676939</v>
+        <v>119676947</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>90846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887530</v>
+        <v>887690</v>
       </c>
       <c r="R13" t="n">
         <v>7417856</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676947</v>
+        <v>119676939</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887690</v>
+        <v>887530</v>
       </c>
       <c r="R14" t="n">
         <v>7417856</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676972</v>
+        <v>119676976</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887564</v>
+        <v>887509</v>
       </c>
       <c r="R28" t="n">
-        <v>7417841</v>
+        <v>7417861</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676976</v>
+        <v>119676972</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887509</v>
+        <v>887564</v>
       </c>
       <c r="R29" t="n">
-        <v>7417861</v>
+        <v>7417841</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676977</v>
+        <v>119676966</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887608</v>
+        <v>887446</v>
       </c>
       <c r="R39" t="n">
-        <v>7417884</v>
+        <v>7417848</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676975</v>
+        <v>119676970</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887451</v>
+        <v>887373</v>
       </c>
       <c r="R40" t="n">
-        <v>7417867</v>
+        <v>7417870</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676966</v>
+        <v>119676977</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4665,25 +4665,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887446</v>
+        <v>887608</v>
       </c>
       <c r="R41" t="n">
-        <v>7417848</v>
+        <v>7417884</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676970</v>
+        <v>119676975</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4767,25 +4767,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887373</v>
+        <v>887451</v>
       </c>
       <c r="R42" t="n">
-        <v>7417870</v>
+        <v>7417867</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676958</v>
+        <v>119676968</v>
       </c>
       <c r="B22" t="n">
-        <v>79643</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887619</v>
+        <v>887375</v>
       </c>
       <c r="R22" t="n">
-        <v>7417836</v>
+        <v>7417827</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676957</v>
+        <v>119676953</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887564</v>
+        <v>887516</v>
       </c>
       <c r="R23" t="n">
-        <v>7417841</v>
+        <v>7417853</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676956</v>
+        <v>119676979</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887549</v>
+        <v>887276</v>
       </c>
       <c r="R24" t="n">
-        <v>7417845</v>
+        <v>7417801</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676964</v>
+        <v>119676966</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887527</v>
+        <v>887446</v>
       </c>
       <c r="R25" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676968</v>
+        <v>119676961</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887375</v>
+        <v>887272</v>
       </c>
       <c r="R26" t="n">
-        <v>7417827</v>
+        <v>7417781</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676971</v>
+        <v>119676970</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887491</v>
+        <v>887373</v>
       </c>
       <c r="R27" t="n">
-        <v>7417873</v>
+        <v>7417870</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676976</v>
+        <v>119676958</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>79659</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887509</v>
+        <v>887619</v>
       </c>
       <c r="R28" t="n">
-        <v>7417861</v>
+        <v>7417836</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676972</v>
+        <v>119676977</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887564</v>
+        <v>887608</v>
       </c>
       <c r="R29" t="n">
-        <v>7417841</v>
+        <v>7417884</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676963</v>
+        <v>119676972</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887685</v>
+        <v>887564</v>
       </c>
       <c r="R30" t="n">
-        <v>7417879</v>
+        <v>7417841</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676953</v>
+        <v>119676959</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>79659</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3645,25 +3645,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887516</v>
+        <v>887484</v>
       </c>
       <c r="R31" t="n">
-        <v>7417853</v>
+        <v>7417813</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119676961</v>
+        <v>119676964</v>
       </c>
       <c r="B32" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3747,25 +3747,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887272</v>
+        <v>887527</v>
       </c>
       <c r="R32" t="n">
-        <v>7417781</v>
+        <v>7417856</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119676973</v>
+        <v>119676967</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887588</v>
+        <v>887389</v>
       </c>
       <c r="R33" t="n">
-        <v>7417887</v>
+        <v>7417834</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119676959</v>
+        <v>119676957</v>
       </c>
       <c r="B34" t="n">
-        <v>79643</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3951,25 +3951,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887484</v>
+        <v>887564</v>
       </c>
       <c r="R34" t="n">
-        <v>7417813</v>
+        <v>7417841</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119676969</v>
+        <v>119676974</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4053,25 +4053,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887366</v>
+        <v>887376</v>
       </c>
       <c r="R35" t="n">
-        <v>7417866</v>
+        <v>7417815</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119676979</v>
+        <v>119676973</v>
       </c>
       <c r="B36" t="n">
-        <v>78171</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4155,25 +4155,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887276</v>
+        <v>887588</v>
       </c>
       <c r="R36" t="n">
-        <v>7417801</v>
+        <v>7417887</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4248,7 +4248,7 @@
         <v>119676954</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119676974</v>
+        <v>119676975</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887376</v>
+        <v>887451</v>
       </c>
       <c r="R38" t="n">
-        <v>7417815</v>
+        <v>7417867</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676966</v>
+        <v>119676976</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,25 +4461,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887446</v>
+        <v>887509</v>
       </c>
       <c r="R39" t="n">
-        <v>7417848</v>
+        <v>7417861</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676970</v>
+        <v>119676963</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887373</v>
+        <v>887685</v>
       </c>
       <c r="R40" t="n">
-        <v>7417870</v>
+        <v>7417879</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676977</v>
+        <v>119676956</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887608</v>
+        <v>887549</v>
       </c>
       <c r="R41" t="n">
-        <v>7417884</v>
+        <v>7417845</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676975</v>
+        <v>119676960</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887451</v>
+        <v>887308</v>
       </c>
       <c r="R42" t="n">
-        <v>7417867</v>
+        <v>7417790</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119676960</v>
+        <v>119676971</v>
       </c>
       <c r="B43" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4869,25 +4869,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887308</v>
+        <v>887491</v>
       </c>
       <c r="R43" t="n">
-        <v>7417790</v>
+        <v>7417873</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119676967</v>
+        <v>119676969</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887389</v>
+        <v>887366</v>
       </c>
       <c r="R44" t="n">
-        <v>7417834</v>
+        <v>7417866</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676959</v>
+        <v>119676964</v>
       </c>
       <c r="B31" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3645,25 +3645,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887484</v>
+        <v>887527</v>
       </c>
       <c r="R31" t="n">
-        <v>7417813</v>
+        <v>7417856</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119676964</v>
+        <v>119676967</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887527</v>
+        <v>887389</v>
       </c>
       <c r="R32" t="n">
-        <v>7417856</v>
+        <v>7417834</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119676967</v>
+        <v>119676959</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>79659</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3849,25 +3849,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887389</v>
+        <v>887484</v>
       </c>
       <c r="R33" t="n">
-        <v>7417834</v>
+        <v>7417813</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676968</v>
+        <v>119676960</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887375</v>
+        <v>887308</v>
       </c>
       <c r="R22" t="n">
-        <v>7417827</v>
+        <v>7417790</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676953</v>
+        <v>119676959</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887516</v>
+        <v>887484</v>
       </c>
       <c r="R23" t="n">
-        <v>7417853</v>
+        <v>7417813</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676979</v>
+        <v>119676968</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887276</v>
+        <v>887375</v>
       </c>
       <c r="R24" t="n">
-        <v>7417801</v>
+        <v>7417827</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676966</v>
+        <v>119676973</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887446</v>
+        <v>887588</v>
       </c>
       <c r="R25" t="n">
-        <v>7417848</v>
+        <v>7417887</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676961</v>
+        <v>119676967</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887272</v>
+        <v>887389</v>
       </c>
       <c r="R26" t="n">
-        <v>7417781</v>
+        <v>7417834</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676970</v>
+        <v>119676953</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887373</v>
+        <v>887516</v>
       </c>
       <c r="R27" t="n">
-        <v>7417870</v>
+        <v>7417853</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676958</v>
+        <v>119676974</v>
       </c>
       <c r="B28" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887619</v>
+        <v>887376</v>
       </c>
       <c r="R28" t="n">
-        <v>7417836</v>
+        <v>7417815</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676977</v>
+        <v>119676976</v>
       </c>
       <c r="B29" t="n">
         <v>78542</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887608</v>
+        <v>887509</v>
       </c>
       <c r="R29" t="n">
-        <v>7417884</v>
+        <v>7417861</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676972</v>
+        <v>119676971</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887564</v>
+        <v>887491</v>
       </c>
       <c r="R30" t="n">
-        <v>7417841</v>
+        <v>7417873</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119676967</v>
+        <v>119676966</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887389</v>
+        <v>887446</v>
       </c>
       <c r="R32" t="n">
-        <v>7417834</v>
+        <v>7417848</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119676959</v>
+        <v>119676977</v>
       </c>
       <c r="B33" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3849,25 +3849,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887484</v>
+        <v>887608</v>
       </c>
       <c r="R33" t="n">
-        <v>7417813</v>
+        <v>7417884</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119676974</v>
+        <v>119676970</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4053,25 +4053,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887376</v>
+        <v>887373</v>
       </c>
       <c r="R35" t="n">
-        <v>7417815</v>
+        <v>7417870</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119676973</v>
+        <v>119676975</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4155,25 +4155,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887588</v>
+        <v>887451</v>
       </c>
       <c r="R36" t="n">
-        <v>7417887</v>
+        <v>7417867</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119676954</v>
+        <v>119676958</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887529</v>
+        <v>887619</v>
       </c>
       <c r="R37" t="n">
-        <v>7417855</v>
+        <v>7417836</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119676975</v>
+        <v>119676972</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4359,25 +4359,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887451</v>
+        <v>887564</v>
       </c>
       <c r="R38" t="n">
-        <v>7417867</v>
+        <v>7417841</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119676976</v>
+        <v>119676961</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887509</v>
+        <v>887272</v>
       </c>
       <c r="R39" t="n">
-        <v>7417861</v>
+        <v>7417781</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4551,7 +4551,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119676963</v>
+        <v>119676969</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887685</v>
+        <v>887366</v>
       </c>
       <c r="R40" t="n">
-        <v>7417879</v>
+        <v>7417866</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119676956</v>
+        <v>119676979</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887549</v>
+        <v>887276</v>
       </c>
       <c r="R41" t="n">
-        <v>7417845</v>
+        <v>7417801</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119676960</v>
+        <v>119676956</v>
       </c>
       <c r="B42" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887308</v>
+        <v>887549</v>
       </c>
       <c r="R42" t="n">
-        <v>7417790</v>
+        <v>7417845</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119676971</v>
+        <v>119676963</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887491</v>
+        <v>887685</v>
       </c>
       <c r="R43" t="n">
-        <v>7417873</v>
+        <v>7417879</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119676969</v>
+        <v>119676954</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4971,25 +4971,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887366</v>
+        <v>887529</v>
       </c>
       <c r="R44" t="n">
-        <v>7417866</v>
+        <v>7417855</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -6646,10 +6646,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121078052</v>
+        <v>121078039</v>
       </c>
       <c r="B59" t="n">
-        <v>91127</v>
+        <v>79679</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6658,31 +6658,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -6693,13 +6693,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>887565</v>
+        <v>887617</v>
       </c>
       <c r="R59" t="n">
-        <v>7417876</v>
+        <v>7417869</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6729,6 +6729,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6756,10 +6761,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121078039</v>
+        <v>121078052</v>
       </c>
       <c r="B60" t="n">
-        <v>79679</v>
+        <v>91127</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6768,31 +6773,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -6803,13 +6808,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>887617</v>
+        <v>887565</v>
       </c>
       <c r="R60" t="n">
-        <v>7417869</v>
+        <v>7417876</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6839,11 +6844,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121071004</v>
+        <v>121073670</v>
       </c>
       <c r="B45" t="n">
-        <v>90523</v>
+        <v>98081</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5073,34 +5073,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6020</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5108,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>887647</v>
+        <v>887645</v>
       </c>
       <c r="R45" t="n">
-        <v>7417877</v>
+        <v>7417840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5164,17 +5165,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121073688</v>
+        <v>121071006</v>
       </c>
       <c r="B46" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5183,35 +5184,34 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>887562</v>
+        <v>887647</v>
       </c>
       <c r="R46" t="n">
-        <v>7417844</v>
+        <v>7417877</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,17 +5275,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121073670</v>
+        <v>121073697</v>
       </c>
       <c r="B47" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>887645</v>
+        <v>887594</v>
       </c>
       <c r="R47" t="n">
-        <v>7417840</v>
+        <v>7417878</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121071006</v>
+        <v>121073688</v>
       </c>
       <c r="B48" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5405,34 +5405,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5440,10 +5441,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>887647</v>
+        <v>887562</v>
       </c>
       <c r="R48" t="n">
-        <v>7417877</v>
+        <v>7417844</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5496,17 +5497,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121073697</v>
+        <v>121071004</v>
       </c>
       <c r="B49" t="n">
-        <v>98071</v>
+        <v>90533</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5515,35 +5516,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6020</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>887594</v>
+        <v>887647</v>
       </c>
       <c r="R49" t="n">
-        <v>7417878</v>
+        <v>7417877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
         <v>121073675</v>
       </c>
       <c r="B50" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5725,10 +5725,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121078050</v>
+        <v>121078029</v>
       </c>
       <c r="B51" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5741,21 +5741,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>887565</v>
+        <v>887652</v>
       </c>
       <c r="R51" t="n">
-        <v>7417876</v>
+        <v>7417884</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5835,10 +5835,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121078001</v>
+        <v>121078039</v>
       </c>
       <c r="B52" t="n">
-        <v>90701</v>
+        <v>79682</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5851,27 +5851,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -5882,13 +5882,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>887708</v>
+        <v>887617</v>
       </c>
       <c r="R52" t="n">
-        <v>7417888</v>
+        <v>7417869</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5918,6 +5918,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5945,10 +5950,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121086081</v>
+        <v>121079199</v>
       </c>
       <c r="B53" t="n">
-        <v>98071</v>
+        <v>82385</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5957,35 +5962,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5993,10 +5997,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>887336</v>
+        <v>887565</v>
       </c>
       <c r="R53" t="n">
-        <v>7417848</v>
+        <v>7417879</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6027,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6056,10 +6060,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121073782</v>
+        <v>121078005</v>
       </c>
       <c r="B54" t="n">
-        <v>79679</v>
+        <v>57367</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6072,30 +6076,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6103,13 +6108,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>887556</v>
+        <v>887669</v>
       </c>
       <c r="R54" t="n">
-        <v>7417840</v>
+        <v>7417851</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6143,7 +6148,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>rikligt på urgammal jättesälg</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6152,39 +6157,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Lågörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>gammal naturskog gran, björk, tall, sälg och asp</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>urgammal jättesälg</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea # urgammal jättesälg</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6194,17 +6168,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121078062</v>
+        <v>121078050</v>
       </c>
       <c r="B55" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6217,27 +6191,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -6248,10 +6222,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>887568</v>
+        <v>887565</v>
       </c>
       <c r="R55" t="n">
-        <v>7417883</v>
+        <v>7417876</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6311,10 +6285,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121078005</v>
+        <v>121086081</v>
       </c>
       <c r="B56" t="n">
-        <v>57364</v>
+        <v>98081</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6323,35 +6297,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6359,13 +6333,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>887669</v>
+        <v>887336</v>
       </c>
       <c r="R56" t="n">
-        <v>7417851</v>
+        <v>7417848</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6389,17 +6363,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6408,6 +6377,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6419,17 +6389,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121086144</v>
+        <v>121078052</v>
       </c>
       <c r="B57" t="n">
-        <v>79679</v>
+        <v>91137</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6438,31 +6408,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -6473,10 +6443,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>887422</v>
+        <v>887565</v>
       </c>
       <c r="R57" t="n">
-        <v>7417851</v>
+        <v>7417876</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6503,12 +6473,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6536,10 +6506,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121078029</v>
+        <v>121078062</v>
       </c>
       <c r="B58" t="n">
-        <v>79679</v>
+        <v>90697</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6552,27 +6522,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -6583,10 +6553,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>887652</v>
+        <v>887568</v>
       </c>
       <c r="R58" t="n">
-        <v>7417884</v>
+        <v>7417883</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6646,10 +6616,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121078039</v>
+        <v>121078046</v>
       </c>
       <c r="B59" t="n">
-        <v>79679</v>
+        <v>82385</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6662,27 +6632,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -6693,13 +6663,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>887617</v>
+        <v>887565</v>
       </c>
       <c r="R59" t="n">
-        <v>7417869</v>
+        <v>7417876</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6729,11 +6699,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6761,10 +6726,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121078052</v>
+        <v>121086107</v>
       </c>
       <c r="B60" t="n">
-        <v>91127</v>
+        <v>98081</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6777,30 +6742,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6808,13 +6774,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>887565</v>
+        <v>887439</v>
       </c>
       <c r="R60" t="n">
-        <v>7417876</v>
+        <v>7417859</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6838,12 +6804,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6864,17 +6830,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121078046</v>
+        <v>121086144</v>
       </c>
       <c r="B61" t="n">
-        <v>82382</v>
+        <v>79682</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6887,27 +6853,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -6918,10 +6884,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>887565</v>
+        <v>887422</v>
       </c>
       <c r="R61" t="n">
-        <v>7417876</v>
+        <v>7417851</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6948,12 +6914,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6981,10 +6947,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121079199</v>
+        <v>121073782</v>
       </c>
       <c r="B62" t="n">
-        <v>82382</v>
+        <v>79682</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6997,27 +6963,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -7028,10 +6994,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>887565</v>
+        <v>887556</v>
       </c>
       <c r="R62" t="n">
-        <v>7417879</v>
+        <v>7417840</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7066,6 +7032,11 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>rikligt på urgammal jättesälg</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7075,6 +7046,36 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>gammal naturskog gran, björk, tall, sälg och asp</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>urgammal jättesälg</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea # urgammal jättesälg</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7091,10 +7092,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121086107</v>
+        <v>121086153</v>
       </c>
       <c r="B63" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7103,35 +7104,34 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7139,13 +7139,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>887439</v>
+        <v>887422</v>
       </c>
       <c r="R63" t="n">
-        <v>7417859</v>
+        <v>7417851</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7195,17 +7195,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121086153</v>
+        <v>121078001</v>
       </c>
       <c r="B64" t="n">
-        <v>78598</v>
+        <v>90711</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7218,27 +7218,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>887422</v>
+        <v>887708</v>
       </c>
       <c r="R64" t="n">
-        <v>7417851</v>
+        <v>7417888</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7315,7 +7315,7 @@
         <v>121086079</v>
       </c>
       <c r="B65" t="n">
-        <v>91996</v>
+        <v>92006</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -6285,10 +6285,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121086081</v>
+        <v>121078052</v>
       </c>
       <c r="B56" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6301,31 +6301,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6333,13 +6332,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>887336</v>
+        <v>887565</v>
       </c>
       <c r="R56" t="n">
-        <v>7417848</v>
+        <v>7417876</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6363,12 +6362,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6389,17 +6388,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121078052</v>
+        <v>121078062</v>
       </c>
       <c r="B57" t="n">
-        <v>91137</v>
+        <v>90697</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6408,25 +6407,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6443,10 +6442,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>887565</v>
+        <v>887568</v>
       </c>
       <c r="R57" t="n">
-        <v>7417876</v>
+        <v>7417883</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6506,10 +6505,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121078062</v>
+        <v>121086081</v>
       </c>
       <c r="B58" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6518,34 +6517,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>887568</v>
+        <v>887336</v>
       </c>
       <c r="R58" t="n">
-        <v>7417883</v>
+        <v>7417848</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -5061,7 +5061,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121073670</v>
+        <v>121073688</v>
       </c>
       <c r="B45" t="n">
         <v>98081</v>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>887645</v>
+        <v>887562</v>
       </c>
       <c r="R45" t="n">
-        <v>7417840</v>
+        <v>7417844</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,10 +5172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121071006</v>
+        <v>121073670</v>
       </c>
       <c r="B46" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5184,34 +5184,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5219,10 +5220,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>887647</v>
+        <v>887645</v>
       </c>
       <c r="R46" t="n">
-        <v>7417877</v>
+        <v>7417840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5275,17 +5276,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121073697</v>
+        <v>121071004</v>
       </c>
       <c r="B47" t="n">
-        <v>98081</v>
+        <v>90533</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5294,35 +5295,34 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6020</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>887594</v>
+        <v>887647</v>
       </c>
       <c r="R47" t="n">
-        <v>7417878</v>
+        <v>7417877</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,14 +5386,14 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121073688</v>
+        <v>121073675</v>
       </c>
       <c r="B48" t="n">
         <v>98081</v>
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>887562</v>
+        <v>887667</v>
       </c>
       <c r="R48" t="n">
-        <v>7417844</v>
+        <v>7417863</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,10 +5504,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121071004</v>
+        <v>121073697</v>
       </c>
       <c r="B49" t="n">
-        <v>90533</v>
+        <v>98081</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5516,34 +5516,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6020</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5551,10 +5552,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>887647</v>
+        <v>887594</v>
       </c>
       <c r="R49" t="n">
-        <v>7417877</v>
+        <v>7417878</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,17 +5608,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121073675</v>
+        <v>121071006</v>
       </c>
       <c r="B50" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5626,35 +5627,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>887667</v>
+        <v>887647</v>
       </c>
       <c r="R50" t="n">
-        <v>7417863</v>
+        <v>7417877</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121078029</v>
+        <v>121078046</v>
       </c>
       <c r="B51" t="n">
-        <v>79682</v>
+        <v>82385</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5741,27 +5741,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>887652</v>
+        <v>887565</v>
       </c>
       <c r="R51" t="n">
-        <v>7417884</v>
+        <v>7417876</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5835,10 +5835,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121078039</v>
+        <v>121078050</v>
       </c>
       <c r="B52" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5851,21 +5851,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5882,13 +5882,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>887617</v>
+        <v>887565</v>
       </c>
       <c r="R52" t="n">
-        <v>7417869</v>
+        <v>7417876</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5918,11 +5918,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5950,10 +5945,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121079199</v>
+        <v>121073797</v>
       </c>
       <c r="B53" t="n">
-        <v>82385</v>
+        <v>79682</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5966,27 +5961,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -5997,10 +5992,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>887565</v>
+        <v>887556</v>
       </c>
       <c r="R53" t="n">
-        <v>7417879</v>
+        <v>7417840</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6035,6 +6030,11 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>rikligt på en liten gran!</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6044,6 +6044,36 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>naturskog med gran, björk, tall, sälg och asp</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>liten gran</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies # liten gran</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6060,10 +6090,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121078005</v>
+        <v>121086153</v>
       </c>
       <c r="B54" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6076,31 +6106,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6108,7 +6137,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>887669</v>
+        <v>887422</v>
       </c>
       <c r="R54" t="n">
         <v>7417851</v>
@@ -6138,17 +6167,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6157,6 +6181,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6175,10 +6200,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121078050</v>
+        <v>121078052</v>
       </c>
       <c r="B55" t="n">
-        <v>78601</v>
+        <v>91137</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6187,31 +6212,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -6285,10 +6310,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121078052</v>
+        <v>121086107</v>
       </c>
       <c r="B56" t="n">
-        <v>91137</v>
+        <v>98081</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6301,30 +6326,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6332,13 +6358,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>887565</v>
+        <v>887439</v>
       </c>
       <c r="R56" t="n">
-        <v>7417876</v>
+        <v>7417859</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6362,12 +6388,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6388,17 +6414,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121078062</v>
+        <v>121086144</v>
       </c>
       <c r="B57" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6411,27 +6437,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -6442,10 +6468,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>887568</v>
+        <v>887422</v>
       </c>
       <c r="R57" t="n">
-        <v>7417883</v>
+        <v>7417851</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6472,12 +6498,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6616,7 +6642,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121078046</v>
+        <v>121079199</v>
       </c>
       <c r="B59" t="n">
         <v>82385</v>
@@ -6666,10 +6692,10 @@
         <v>887565</v>
       </c>
       <c r="R59" t="n">
-        <v>7417876</v>
+        <v>7417879</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6719,17 +6745,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121086107</v>
+        <v>121078001</v>
       </c>
       <c r="B60" t="n">
-        <v>98081</v>
+        <v>90711</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6738,35 +6764,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6774,13 +6799,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>887439</v>
+        <v>887708</v>
       </c>
       <c r="R60" t="n">
-        <v>7417859</v>
+        <v>7417888</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6804,12 +6829,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6830,14 +6855,14 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121086144</v>
+        <v>121078039</v>
       </c>
       <c r="B61" t="n">
         <v>79682</v>
@@ -6884,13 +6909,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>887422</v>
+        <v>887617</v>
       </c>
       <c r="R61" t="n">
-        <v>7417851</v>
+        <v>7417869</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6914,12 +6939,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6947,7 +6977,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121073782</v>
+        <v>121078029</v>
       </c>
       <c r="B62" t="n">
         <v>79682</v>
@@ -6994,13 +7024,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>887556</v>
+        <v>887652</v>
       </c>
       <c r="R62" t="n">
-        <v>7417840</v>
+        <v>7417884</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7030,11 +7060,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>rikligt på urgammal jättesälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7047,36 +7072,6 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Lågörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>gammal naturskog gran, björk, tall, sälg och asp</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>urgammal jättesälg</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea # urgammal jättesälg</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7085,17 +7080,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121086153</v>
+        <v>121078005</v>
       </c>
       <c r="B63" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7108,30 +7103,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7139,7 +7135,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>887422</v>
+        <v>887669</v>
       </c>
       <c r="R63" t="n">
         <v>7417851</v>
@@ -7169,12 +7165,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7183,7 +7184,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7202,10 +7202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121078001</v>
+        <v>121078062</v>
       </c>
       <c r="B64" t="n">
-        <v>90711</v>
+        <v>90697</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7218,21 +7218,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>887708</v>
+        <v>887568</v>
       </c>
       <c r="R64" t="n">
-        <v>7417888</v>
+        <v>7417883</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121073688</v>
+        <v>121071006</v>
       </c>
       <c r="B45" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5073,35 +5073,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5109,10 +5108,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>887562</v>
+        <v>887647</v>
       </c>
       <c r="R45" t="n">
-        <v>7417844</v>
+        <v>7417877</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5165,7 +5164,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5175,7 +5174,7 @@
         <v>121073670</v>
       </c>
       <c r="B46" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5283,10 +5282,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121071004</v>
+        <v>121073688</v>
       </c>
       <c r="B47" t="n">
-        <v>90533</v>
+        <v>98094</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5295,34 +5294,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6020</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>887647</v>
+        <v>887562</v>
       </c>
       <c r="R47" t="n">
-        <v>7417877</v>
+        <v>7417844</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,17 +5386,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121073675</v>
+        <v>121071004</v>
       </c>
       <c r="B48" t="n">
-        <v>98081</v>
+        <v>90545</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5405,35 +5405,34 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6020</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5441,10 +5440,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>887667</v>
+        <v>887647</v>
       </c>
       <c r="R48" t="n">
-        <v>7417863</v>
+        <v>7417877</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5507,7 +5506,7 @@
         <v>121073697</v>
       </c>
       <c r="B49" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,10 +5614,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121071006</v>
+        <v>121073675</v>
       </c>
       <c r="B50" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5627,34 +5626,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>887647</v>
+        <v>887667</v>
       </c>
       <c r="R50" t="n">
-        <v>7417877</v>
+        <v>7417863</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121078046</v>
+        <v>121086153</v>
       </c>
       <c r="B51" t="n">
-        <v>82385</v>
+        <v>78604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5741,27 +5741,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>887565</v>
+        <v>887422</v>
       </c>
       <c r="R51" t="n">
-        <v>7417876</v>
+        <v>7417851</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5835,10 +5835,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121078050</v>
+        <v>121078005</v>
       </c>
       <c r="B52" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5851,30 +5851,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5882,10 +5883,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>887565</v>
+        <v>887669</v>
       </c>
       <c r="R52" t="n">
-        <v>7417876</v>
+        <v>7417851</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5920,13 +5921,17 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5945,10 +5950,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121073797</v>
+        <v>121079199</v>
       </c>
       <c r="B53" t="n">
-        <v>79682</v>
+        <v>82388</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,27 +5966,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -5992,10 +5997,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>887556</v>
+        <v>887565</v>
       </c>
       <c r="R53" t="n">
-        <v>7417840</v>
+        <v>7417879</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6030,11 +6035,6 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>rikligt på en liten gran!</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6044,36 +6044,6 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Lågörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>naturskog med gran, björk, tall, sälg och asp</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>liten gran</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies # liten gran</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6090,10 +6060,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121086153</v>
+        <v>121073797</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6106,21 +6076,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6137,13 +6107,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>887422</v>
+        <v>887556</v>
       </c>
       <c r="R54" t="n">
-        <v>7417851</v>
+        <v>7417840</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6167,12 +6137,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>rikligt på en liten gran!</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6185,6 +6160,36 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>naturskog med gran, björk, tall, sälg och asp</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>liten gran</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies # liten gran</t>
+        </is>
+      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
@@ -6193,17 +6198,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121078052</v>
+        <v>121078062</v>
       </c>
       <c r="B55" t="n">
-        <v>91137</v>
+        <v>90709</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6212,25 +6217,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6247,10 +6252,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>887565</v>
+        <v>887568</v>
       </c>
       <c r="R55" t="n">
-        <v>7417876</v>
+        <v>7417883</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6310,10 +6315,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121086107</v>
+        <v>121078046</v>
       </c>
       <c r="B56" t="n">
-        <v>98081</v>
+        <v>82388</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6322,35 +6327,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6358,13 +6362,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>887439</v>
+        <v>887565</v>
       </c>
       <c r="R56" t="n">
-        <v>7417859</v>
+        <v>7417876</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6388,12 +6392,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6414,17 +6418,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121086144</v>
+        <v>121078039</v>
       </c>
       <c r="B57" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6468,13 +6472,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>887422</v>
+        <v>887617</v>
       </c>
       <c r="R57" t="n">
-        <v>7417851</v>
+        <v>7417869</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6498,12 +6502,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6531,10 +6540,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121086081</v>
+        <v>121078052</v>
       </c>
       <c r="B58" t="n">
-        <v>98081</v>
+        <v>91149</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6547,31 +6556,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6579,13 +6587,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>887336</v>
+        <v>887565</v>
       </c>
       <c r="R58" t="n">
-        <v>7417848</v>
+        <v>7417876</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6609,12 +6617,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6635,17 +6643,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121079199</v>
+        <v>121078001</v>
       </c>
       <c r="B59" t="n">
-        <v>82385</v>
+        <v>90723</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6658,21 +6666,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6689,13 +6697,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>887565</v>
+        <v>887708</v>
       </c>
       <c r="R59" t="n">
-        <v>7417879</v>
+        <v>7417888</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6745,17 +6753,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121078001</v>
+        <v>121086081</v>
       </c>
       <c r="B60" t="n">
-        <v>90711</v>
+        <v>98094</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6764,34 +6772,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6799,13 +6808,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>887708</v>
+        <v>887336</v>
       </c>
       <c r="R60" t="n">
-        <v>7417888</v>
+        <v>7417848</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6829,12 +6838,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6855,17 +6864,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121078039</v>
+        <v>121086144</v>
       </c>
       <c r="B61" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6909,13 +6918,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>887617</v>
+        <v>887422</v>
       </c>
       <c r="R61" t="n">
-        <v>7417869</v>
+        <v>7417851</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6939,17 +6948,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>på en död sälg</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6977,10 +6981,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121078029</v>
+        <v>121086107</v>
       </c>
       <c r="B62" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6989,34 +6993,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7024,13 +7029,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>887652</v>
+        <v>887439</v>
       </c>
       <c r="R62" t="n">
-        <v>7417884</v>
+        <v>7417859</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7054,12 +7059,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7080,17 +7085,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121078005</v>
+        <v>121078050</v>
       </c>
       <c r="B63" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7103,31 +7108,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7135,10 +7139,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>887669</v>
+        <v>887565</v>
       </c>
       <c r="R63" t="n">
-        <v>7417851</v>
+        <v>7417876</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7173,17 +7177,13 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7202,10 +7202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121078062</v>
+        <v>121078029</v>
       </c>
       <c r="B64" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7218,27 +7218,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>887568</v>
+        <v>887652</v>
       </c>
       <c r="R64" t="n">
-        <v>7417883</v>
+        <v>7417884</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7315,7 +7315,7 @@
         <v>121086079</v>
       </c>
       <c r="B65" t="n">
-        <v>92006</v>
+        <v>92018</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -5725,10 +5725,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121086153</v>
+        <v>121079199</v>
       </c>
       <c r="B51" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5741,27 +5741,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>887422</v>
+        <v>887565</v>
       </c>
       <c r="R51" t="n">
-        <v>7417851</v>
+        <v>7417879</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5828,17 +5828,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121078005</v>
+        <v>121078029</v>
       </c>
       <c r="B52" t="n">
-        <v>57367</v>
+        <v>79685</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5851,31 +5851,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5883,10 +5882,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>887669</v>
+        <v>887652</v>
       </c>
       <c r="R52" t="n">
-        <v>7417851</v>
+        <v>7417884</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5921,17 +5920,13 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5950,10 +5945,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121079199</v>
+        <v>121086081</v>
       </c>
       <c r="B53" t="n">
-        <v>82388</v>
+        <v>98095</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5962,34 +5957,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5997,10 +5993,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>887565</v>
+        <v>887336</v>
       </c>
       <c r="R53" t="n">
-        <v>7417879</v>
+        <v>7417848</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6027,12 +6023,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6060,10 +6056,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121073797</v>
+        <v>121078001</v>
       </c>
       <c r="B54" t="n">
-        <v>79685</v>
+        <v>90724</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6076,27 +6072,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -6107,13 +6103,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>887556</v>
+        <v>887708</v>
       </c>
       <c r="R54" t="n">
-        <v>7417840</v>
+        <v>7417888</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6143,11 +6139,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>rikligt på en liten gran!</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6160,36 +6151,6 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Lågörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>naturskog med gran, björk, tall, sälg och asp</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>liten gran</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies # liten gran</t>
-        </is>
-      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
@@ -6198,17 +6159,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121078062</v>
+        <v>121078046</v>
       </c>
       <c r="B55" t="n">
-        <v>90709</v>
+        <v>82388</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6221,21 +6182,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6252,10 +6213,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>887568</v>
+        <v>887565</v>
       </c>
       <c r="R55" t="n">
-        <v>7417883</v>
+        <v>7417876</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6315,10 +6276,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121078046</v>
+        <v>121086153</v>
       </c>
       <c r="B56" t="n">
-        <v>82388</v>
+        <v>78604</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6331,27 +6292,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -6362,10 +6323,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>887565</v>
+        <v>887422</v>
       </c>
       <c r="R56" t="n">
-        <v>7417876</v>
+        <v>7417851</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6392,12 +6353,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6425,7 +6386,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121078039</v>
+        <v>121086144</v>
       </c>
       <c r="B57" t="n">
         <v>79685</v>
@@ -6472,13 +6433,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>887617</v>
+        <v>887422</v>
       </c>
       <c r="R57" t="n">
-        <v>7417869</v>
+        <v>7417851</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6502,17 +6463,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>på en död sälg</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6540,10 +6496,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121078052</v>
+        <v>121073782</v>
       </c>
       <c r="B58" t="n">
-        <v>91149</v>
+        <v>79685</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6552,31 +6508,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -6587,13 +6543,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>887565</v>
+        <v>887556</v>
       </c>
       <c r="R58" t="n">
-        <v>7417876</v>
+        <v>7417840</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6623,6 +6579,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>rikligt på urgammal jättesälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6635,6 +6596,36 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>gammal naturskog gran, björk, tall, sälg och asp</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>urgammal jättesälg</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Salix caprea # urgammal jättesälg</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
@@ -6643,17 +6634,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121078001</v>
+        <v>121078005</v>
       </c>
       <c r="B59" t="n">
-        <v>90723</v>
+        <v>57367</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6666,30 +6657,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6697,10 +6689,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>887708</v>
+        <v>887669</v>
       </c>
       <c r="R59" t="n">
-        <v>7417888</v>
+        <v>7417851</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6735,13 +6727,17 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6760,10 +6756,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121086081</v>
+        <v>121078052</v>
       </c>
       <c r="B60" t="n">
-        <v>98094</v>
+        <v>91150</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6776,31 +6772,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6808,13 +6803,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>887336</v>
+        <v>887565</v>
       </c>
       <c r="R60" t="n">
-        <v>7417848</v>
+        <v>7417876</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6838,12 +6833,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6864,17 +6859,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121086144</v>
+        <v>121086107</v>
       </c>
       <c r="B61" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6883,34 +6878,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6918,13 +6914,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>887422</v>
+        <v>887439</v>
       </c>
       <c r="R61" t="n">
-        <v>7417851</v>
+        <v>7417859</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6974,17 +6970,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121086107</v>
+        <v>121078050</v>
       </c>
       <c r="B62" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6993,35 +6989,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7029,13 +7024,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>887439</v>
+        <v>887565</v>
       </c>
       <c r="R62" t="n">
-        <v>7417859</v>
+        <v>7417876</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7059,12 +7054,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7085,17 +7080,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121078050</v>
+        <v>121078062</v>
       </c>
       <c r="B63" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7108,27 +7103,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -7139,10 +7134,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>887565</v>
+        <v>887568</v>
       </c>
       <c r="R63" t="n">
-        <v>7417876</v>
+        <v>7417883</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7202,7 +7197,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121078029</v>
+        <v>121078039</v>
       </c>
       <c r="B64" t="n">
         <v>79685</v>
@@ -7249,13 +7244,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>887652</v>
+        <v>887617</v>
       </c>
       <c r="R64" t="n">
-        <v>7417884</v>
+        <v>7417869</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7285,6 +7280,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>på en död sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7315,7 +7315,7 @@
         <v>121086079</v>
       </c>
       <c r="B65" t="n">
-        <v>92018</v>
+        <v>92019</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7315,7 +7315,7 @@
         <v>121086079</v>
       </c>
       <c r="B65" t="n">
-        <v>92019</v>
+        <v>92022</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7420,6 +7420,205 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125831643</v>
+      </c>
+      <c r="B66" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>887336</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7417885</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125831647</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>887323</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7417863</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7618,6 +7618,394 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125948990</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>887315</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7417864</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125948991</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>887291</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7417833</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125948977</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92707</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>887257</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7417821</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125948970</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>887288</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7417832</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>125948970</v>
       </c>
       <c r="B71" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92708</v>
+        <v>92710</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>125948970</v>
       </c>
       <c r="B71" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7425,7 +7425,7 @@
         <v>125831643</v>
       </c>
       <c r="B66" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>125948970</v>
       </c>
       <c r="B71" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7425,7 +7425,7 @@
         <v>125831643</v>
       </c>
       <c r="B66" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>125948970</v>
       </c>
       <c r="B71" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -7425,7 +7425,7 @@
         <v>125831643</v>
       </c>
       <c r="B66" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>125831647</v>
       </c>
       <c r="B67" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>125948990</v>
       </c>
       <c r="B68" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>125948991</v>
       </c>
       <c r="B69" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>125948977</v>
       </c>
       <c r="B70" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>125948970</v>
       </c>
       <c r="B71" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29053-2020 artfynd.xlsx
+++ b/artfynd/A 29053-2020 artfynd.xlsx
@@ -8012,7 +8012,7 @@
         <v>126911406</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8110,45 +8110,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126914923</v>
+        <v>126915397</v>
       </c>
       <c r="B73" t="n">
-        <v>56849</v>
+        <v>98436</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Pikku Pulinki mitt, Nb</t>
+          <t>Pikku Pullinki, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>887625</v>
+        <v>887375</v>
       </c>
       <c r="R73" t="n">
-        <v>7417822</v>
+        <v>7417850</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8183,6 +8183,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8195,12 +8200,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Marlene Kangas, Christina Boyd, Petra Wikström, Petya Valcheva, per-erik mukka, Tomas Falk, Cecilia Rastad, Viktoria Sturk, Marie Persson, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8211,45 +8216,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126913698</v>
+        <v>126914923</v>
       </c>
       <c r="B74" t="n">
-        <v>91245</v>
+        <v>56849</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku Pulinki mitt, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>887530</v>
+        <v>887625</v>
       </c>
       <c r="R74" t="n">
-        <v>7417882</v>
+        <v>7417822</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8296,12 +8301,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8312,45 +8317,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126915397</v>
+        <v>126913698</v>
       </c>
       <c r="B75" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Pikku Pullinki, Nb</t>
+          <t>Pikku Pulinki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>887375</v>
+        <v>887530</v>
       </c>
       <c r="R75" t="n">
-        <v>7417850</v>
+        <v>7417882</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8385,11 +8390,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8402,12 +8402,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Christina Boyd, Petra Wikström, Petya Valcheva, per-erik mukka, Tomas Falk, Cecilia Rastad, Viktoria Sturk, Marie Persson, Jenny Hjelm Córdoba</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8418,45 +8418,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126913699</v>
+        <v>126914364</v>
       </c>
       <c r="B76" t="n">
-        <v>91245</v>
+        <v>95293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku pulinki, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>887514</v>
+        <v>887307</v>
       </c>
       <c r="R76" t="n">
-        <v>7417864</v>
+        <v>7417869</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8486,9 +8486,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8503,12 +8513,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8519,45 +8529,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126914364</v>
+        <v>126913699</v>
       </c>
       <c r="B77" t="n">
-        <v>95218</v>
+        <v>91319</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Pikku pulinki, Nb</t>
+          <t>Pikku Pulinki, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>887307</v>
+        <v>887514</v>
       </c>
       <c r="R77" t="n">
-        <v>7417869</v>
+        <v>7417864</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8587,19 +8597,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8614,12 +8614,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8633,7 +8633,7 @@
         <v>126914378</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>126913727</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>126913725</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8943,45 +8943,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126913905</v>
+        <v>126913706</v>
       </c>
       <c r="B81" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Pikku Pullinki, Nb</t>
+          <t>Pikku Pulinki, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>887526</v>
+        <v>887403</v>
       </c>
       <c r="R81" t="n">
-        <v>7417867</v>
+        <v>7417830</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9028,12 +9028,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9044,45 +9044,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126913706</v>
+        <v>126913905</v>
       </c>
       <c r="B82" t="n">
-        <v>80112</v>
+        <v>98436</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku Pullinki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>887403</v>
+        <v>887526</v>
       </c>
       <c r="R82" t="n">
-        <v>7417830</v>
+        <v>7417867</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9129,12 +9129,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9148,7 +9148,7 @@
         <v>126915385</v>
       </c>
       <c r="B83" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9246,32 +9246,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913908</v>
+        <v>126913901</v>
       </c>
       <c r="B84" t="n">
-        <v>98361</v>
+        <v>80150</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>887300</v>
+        <v>887419</v>
       </c>
       <c r="R84" t="n">
-        <v>7417823</v>
+        <v>7417852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9347,32 +9347,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913901</v>
+        <v>126913908</v>
       </c>
       <c r="B85" t="n">
-        <v>80119</v>
+        <v>98436</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>887419</v>
+        <v>887300</v>
       </c>
       <c r="R85" t="n">
-        <v>7417852</v>
+        <v>7417823</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9451,7 +9451,7 @@
         <v>126913907</v>
       </c>
       <c r="B86" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>126914392</v>
       </c>
       <c r="B87" t="n">
-        <v>91655</v>
+        <v>91729</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9660,32 +9660,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126913705</v>
+        <v>126913724</v>
       </c>
       <c r="B88" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>887516</v>
+        <v>887514</v>
       </c>
       <c r="R88" t="n">
-        <v>7417865</v>
+        <v>7417864</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9761,32 +9761,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126913724</v>
+        <v>126913705</v>
       </c>
       <c r="B89" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9796,10 +9796,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>887514</v>
+        <v>887516</v>
       </c>
       <c r="R89" t="n">
-        <v>7417864</v>
+        <v>7417865</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9865,7 +9865,7 @@
         <v>126914336</v>
       </c>
       <c r="B90" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>126913704</v>
       </c>
       <c r="B91" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10074,10 +10074,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126911409</v>
+        <v>126914394</v>
       </c>
       <c r="B92" t="n">
-        <v>98278</v>
+        <v>91284</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10085,21 +10085,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>887414</v>
+        <v>887269</v>
       </c>
       <c r="R92" t="n">
-        <v>7417852</v>
+        <v>7417820</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10142,9 +10142,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10159,12 +10169,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Tomas Falk, Viktoria Sturk, Petra Wikström, Petya Valcheva, Cecilia Rastad, Marlene Kangas, Marie Persson, Jenny Hjelm Córdoba</t>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10175,45 +10185,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126914394</v>
+        <v>126913726</v>
       </c>
       <c r="B93" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Pikku pulinki, Nb</t>
+          <t>Pikku Pulinki, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>887269</v>
+        <v>887378</v>
       </c>
       <c r="R93" t="n">
-        <v>7417820</v>
+        <v>7417841</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10243,19 +10253,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10270,12 +10270,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10286,45 +10286,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126913726</v>
+        <v>126911409</v>
       </c>
       <c r="B94" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku pulinki, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>887378</v>
+        <v>887414</v>
       </c>
       <c r="R94" t="n">
-        <v>7417841</v>
+        <v>7417852</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10371,12 +10371,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Christina Boyd, per-erik mukka, Tomas Falk, Viktoria Sturk, Petra Wikström, Petya Valcheva, Cecilia Rastad, Marlene Kangas, Marie Persson, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10390,7 +10390,7 @@
         <v>126913922</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>126913921</v>
       </c>
       <c r="B96" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10589,45 +10589,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126913714</v>
+        <v>126914924</v>
       </c>
       <c r="B97" t="n">
-        <v>80083</v>
+        <v>56849</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku Pulinki mitt, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>887513</v>
+        <v>887624</v>
       </c>
       <c r="R97" t="n">
-        <v>7417869</v>
+        <v>7417815</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10674,12 +10674,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10690,10 +10690,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126914924</v>
+        <v>126913707</v>
       </c>
       <c r="B98" t="n">
-        <v>56849</v>
+        <v>80143</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10701,34 +10701,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Pikku Pulinki mitt, Nb</t>
+          <t>Pikku Pulinki, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>887624</v>
+        <v>887365</v>
       </c>
       <c r="R98" t="n">
-        <v>7417815</v>
+        <v>7417843</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10775,12 +10775,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10791,32 +10791,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126913707</v>
+        <v>126913714</v>
       </c>
       <c r="B99" t="n">
-        <v>80112</v>
+        <v>80114</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10826,10 +10826,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>887365</v>
+        <v>887513</v>
       </c>
       <c r="R99" t="n">
-        <v>7417843</v>
+        <v>7417869</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10892,45 +10892,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126915398</v>
+        <v>126913742</v>
       </c>
       <c r="B100" t="n">
-        <v>98361</v>
+        <v>80149</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Pikku Pullinki, Nb</t>
+          <t>Pikku Pulinki, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>887364</v>
+        <v>887516</v>
       </c>
       <c r="R100" t="n">
-        <v>7417853</v>
+        <v>7417865</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10965,11 +10965,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -10982,12 +10977,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Christina Boyd, Petra Wikström, Petya Valcheva, per-erik mukka, Tomas Falk, Cecilia Rastad, Viktoria Sturk, Marie Persson, Jenny Hjelm Córdoba</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10998,45 +10993,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126913742</v>
+        <v>126915398</v>
       </c>
       <c r="B101" t="n">
-        <v>80118</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku Pullinki, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>887516</v>
+        <v>887364</v>
       </c>
       <c r="R101" t="n">
-        <v>7417865</v>
+        <v>7417853</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11071,6 +11066,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11083,12 +11083,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Marlene Kangas, Christina Boyd, Petra Wikström, Petya Valcheva, per-erik mukka, Tomas Falk, Cecilia Rastad, Viktoria Sturk, Marie Persson, Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11102,7 +11102,7 @@
         <v>126913900</v>
       </c>
       <c r="B102" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11200,48 +11200,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126915379</v>
+        <v>126913717</v>
       </c>
       <c r="B103" t="n">
-        <v>91245</v>
+        <v>80150</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikku Pulinki, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>887486</v>
+        <v>887370</v>
       </c>
       <c r="R103" t="n">
-        <v>7417823</v>
+        <v>7417838</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11285,12 +11285,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11301,45 +11301,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126913717</v>
+        <v>126914341</v>
       </c>
       <c r="B104" t="n">
-        <v>80119</v>
+        <v>91319</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku pulinki, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>887370</v>
+        <v>887532</v>
       </c>
       <c r="R104" t="n">
-        <v>7417838</v>
+        <v>7417865</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11369,9 +11369,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11386,12 +11396,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11402,10 +11412,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126914341</v>
+        <v>126915379</v>
       </c>
       <c r="B105" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11433,17 +11443,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Pikku pulinki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>887532</v>
+        <v>887486</v>
       </c>
       <c r="R105" t="n">
-        <v>7417865</v>
+        <v>7417823</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11470,19 +11480,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11497,12 +11497,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
